--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N103_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N103_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.65005610512724</v>
+        <v>4.330634117083176</v>
       </c>
       <c r="D2" t="n">
-        <v>35.55310308912957</v>
+        <v>5.777379251983556</v>
       </c>
       <c r="E2" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F2" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.27923958213126</v>
+        <v>3.945376432096331</v>
       </c>
       <c r="D3" t="n">
-        <v>27.20832103922135</v>
+        <v>4.421352168873469</v>
       </c>
       <c r="E3" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F3" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.9271404365152</v>
+        <v>5.83816032093372</v>
       </c>
       <c r="D4" t="n">
-        <v>21.3777294589699</v>
+        <v>3.473881037082609</v>
       </c>
       <c r="E4" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F4" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.99975866039837</v>
+        <v>4.387460782314735</v>
       </c>
       <c r="D5" t="n">
-        <v>9.293067906300442</v>
+        <v>1.510123534773822</v>
       </c>
       <c r="E5" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F5" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.44346604497488</v>
+        <v>4.784563232308418</v>
       </c>
       <c r="D6" t="n">
-        <v>11.34696140397362</v>
+        <v>1.843881228145714</v>
       </c>
       <c r="E6" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F6" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.07025772276812</v>
+        <v>6.186416879949819</v>
       </c>
       <c r="D7" t="n">
-        <v>13.88429476567943</v>
+        <v>2.256197899422907</v>
       </c>
       <c r="E7" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F7" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.21873483626405</v>
+        <v>8.160544410892909</v>
       </c>
       <c r="D8" t="n">
-        <v>11.63453745095555</v>
+        <v>1.890612335780277</v>
       </c>
       <c r="E8" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F8" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.4184135760988</v>
+        <v>6.730492206116055</v>
       </c>
       <c r="D9" t="n">
-        <v>8.450098774107063</v>
+        <v>1.373141050792398</v>
       </c>
       <c r="E9" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F9" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.16898372131143</v>
+        <v>7.014959854713108</v>
       </c>
       <c r="D10" t="n">
-        <v>40.97950119670711</v>
+        <v>6.659168944464906</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F10" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.42739830293353</v>
+        <v>7.706952224226698</v>
       </c>
       <c r="D11" t="n">
-        <v>48.99383331386755</v>
+        <v>7.961497913503477</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F11" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.39845139658688</v>
+        <v>5.752248351945368</v>
       </c>
       <c r="D12" t="n">
-        <v>26.75577620994229</v>
+        <v>4.347813634115622</v>
       </c>
       <c r="E12" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F12" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.77734480245557</v>
+        <v>5.651318530399031</v>
       </c>
       <c r="D13" t="n">
-        <v>37.67867698047591</v>
+        <v>6.122785009327335</v>
       </c>
       <c r="E13" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F13" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.38729636398093</v>
+        <v>3.1504356591469</v>
       </c>
       <c r="D14" t="n">
-        <v>20.65184724187577</v>
+        <v>3.355925176804813</v>
       </c>
       <c r="E14" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F14" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>34.72261176337876</v>
+        <v>5.642424411549048</v>
       </c>
       <c r="D15" t="n">
-        <v>35.67188840546288</v>
+        <v>5.796681865887718</v>
       </c>
       <c r="E15" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F15" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>8.833634675571984</v>
+        <v>1.435465634780448</v>
       </c>
       <c r="D16" t="n">
-        <v>4.103334368703721</v>
+        <v>0.6667918349143547</v>
       </c>
       <c r="E16" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F16" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>10.33221722459954</v>
+        <v>1.678985298997425</v>
       </c>
       <c r="D17" t="n">
-        <v>6.417475002235202</v>
+        <v>1.04283968786322</v>
       </c>
       <c r="E17" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F17" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>28.64553857194329</v>
+        <v>4.654900017940785</v>
       </c>
       <c r="D18" t="n">
-        <v>27.10075344549186</v>
+        <v>4.403872434892429</v>
       </c>
       <c r="E18" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F18" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.09876767687679</v>
+        <v>6.191049747492478</v>
       </c>
       <c r="D19" t="n">
-        <v>37.34472609439411</v>
+        <v>6.068517990339044</v>
       </c>
       <c r="E19" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F19" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.96065643240054</v>
+        <v>3.893606670265088</v>
       </c>
       <c r="D20" t="n">
-        <v>20.5731144856378</v>
+        <v>3.343131103916142</v>
       </c>
       <c r="E20" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F20" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>35.18130983552673</v>
+        <v>5.716962848273093</v>
       </c>
       <c r="D21" t="n">
-        <v>30.96095223916972</v>
+        <v>5.031154738865079</v>
       </c>
       <c r="E21" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F21" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>25.68697531837293</v>
+        <v>4.174133489235602</v>
       </c>
       <c r="D22" t="n">
-        <v>20.26234088261038</v>
+        <v>3.292630393424187</v>
       </c>
       <c r="E22" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F22" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>39.98432365411136</v>
+        <v>6.497452593793096</v>
       </c>
       <c r="D23" t="n">
-        <v>35.12723825039392</v>
+        <v>5.708176215689012</v>
       </c>
       <c r="E23" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F23" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>35.61054066301765</v>
+        <v>5.786712857740369</v>
       </c>
       <c r="D24" t="n">
-        <v>30.42492077009901</v>
+        <v>4.94404962514109</v>
       </c>
       <c r="E24" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F24" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>43.15211672096272</v>
+        <v>7.012218967156442</v>
       </c>
       <c r="D25" t="n">
-        <v>37.88673387754567</v>
+        <v>6.156594255101172</v>
       </c>
       <c r="E25" t="n">
-        <v>10.22231221132757</v>
+        <v>1.661125734340729</v>
       </c>
       <c r="F25" t="n">
-        <v>12.21451410550081</v>
+        <v>1.984858542143882</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
